--- a/ДМАртём.xlsx
+++ b/ДМАртём.xlsx
@@ -70,7 +70,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -105,11 +105,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +150,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,7 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -12367,7 +12362,7 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Состояние плюса</t>
+          <t>Действие</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
